--- a/reviews/a-envoyer/jlawsongolf-2026-10-19.xlsx
+++ b/reviews/a-envoyer/jlawsongolf-2026-10-19.xlsx
@@ -1179,7 +1179,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-16T06:15:53</t>
+          <t>2026-10-16T09:35:22</t>
         </is>
       </c>
     </row>
